--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
   <si>
     <t>49004</t>
   </si>
@@ -162,28 +162,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>DE53BB76C5848ED6A78A93D93428942E</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>5B30609E4D5F27A92B30B00120145ED3</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Unidad de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>En el periodo del 01 de julio del 2022 al 31 de diciembre del 2022 y con fundamento en los artículos 24, 25,26 y 27 de la Ley de Transparencia y Acceso a la Información Pública para el Estado de Tlaxcala,  el Colegio de Bachilleres del Estado de Tlaxcala no emitió dictámenes sobre reserva o clasificación de información como confidencial.</t>
+    <t>Área de transparencia</t>
+  </si>
+  <si>
+    <t>17/04/2023</t>
+  </si>
+  <si>
+    <t>17/07/2023</t>
+  </si>
+  <si>
+    <t>En el periodo del 01 de enero del 2023 al 30 de junio del 2023 y con fundamento en los artículos 24, 25,26 y 27 de la Ley de Transparencia y Acceso a la Información Pública para el Estado de Tlaxcala,  el Colegio de Bachilleres del Estado de Tlaxcala no emitió dictámenes sobre reserva o clasificación de información como confidencial.</t>
   </si>
   <si>
     <t>Ampliación de plazo</t>
@@ -296,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -310,9 +313,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,7 +618,7 @@
   <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -892,10 +892,10 @@
         <v>52</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q8" s="6" t="s">
         <v>53</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -909,13 +909,13 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J201">
       <formula1>Hidden_19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K201">
       <formula1>Hidden_210</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L201">
       <formula1>Hidden_311</formula1>
     </dataValidation>
   </dataValidations>
@@ -930,32 +930,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -970,17 +970,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -995,17 +995,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
